--- a/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19_V18_Structure/01_Audit_Reports/CRO_UX_Findings.xlsx
+++ b/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19_V18_Structure/01_Audit_Reports/CRO_UX_Findings.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R5d339503f1554fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="2" r:id="R32df5247a3534c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRO &amp; UX Findings" sheetId="1" r:id="R4dbf47c4a10d4832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Wins" sheetId="2" r:id="R8874433d203742fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="20"/>
+      <x:sz val="18"/>
       <x:color rgb="FFFFFEFA"/>
       <x:name val="Georgia"/>
     </x:font>
@@ -32,18 +32,18 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF3E4C83"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFEFA"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color rgb="FFFFFEFA"/>
-      <x:name val="Georgia"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +62,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFEFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF3E4C83"/>
       </x:patternFill>
     </x:fill>
@@ -71,27 +76,13 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="1">
     <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -105,14 +96,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -132,7 +126,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Quality controls</a:t>
+              <a:t>Priority distribution</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -146,11 +140,11 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Value</c:v>
+            <c:v>Rows</c:v>
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'Overview'!$A$15:$A$17</c:f>
+              <c:f>'CRO &amp; UX Findings'!$J$6:$J$9</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -158,7 +152,119 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Overview'!$B$15:$B$17</c:f>
+              <c:f>'CRO &amp; UX Findings'!$K$6:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>Priority distribution</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Rows</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Quick Wins'!$J$6:$J$9</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Quick Wins'!$K$6:$K$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="0"/>
@@ -236,15 +342,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -258,7 +364,42 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re24312414183481f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6071e88b24f94c43"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc46eb2b5ad5c44fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -268,17 +409,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CROandUXFindings4" displayName="CROandUXFindings4" ref="A5:H10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H10"/>
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="ID"/>
-    <x:tableColumn id="2" name="Priority"/>
-    <x:tableColumn id="3" name="Category"/>
-    <x:tableColumn id="4" name="Finding"/>
-    <x:tableColumn id="5" name="Impact"/>
-    <x:tableColumn id="6" name="Confidence"/>
-    <x:tableColumn id="7" name="Approval"/>
-    <x:tableColumn id="8" name="Evidence"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CROandUXFindings40" displayName="CROandUXFindings40" ref="A5:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G30"/>
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="Finding ID"/>
+    <x:tableColumn id="2" name="Category"/>
+    <x:tableColumn id="3" name="Finding"/>
+    <x:tableColumn id="4" name="Impact"/>
+    <x:tableColumn id="5" name="Priority"/>
+    <x:tableColumn id="6" name="Recommendation"/>
+    <x:tableColumn id="7" name="Evidence"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CROandUXFindings41" displayName="CROandUXFindings41" ref="A5:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G17"/>
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="Finding ID"/>
+    <x:tableColumn id="2" name="Category"/>
+    <x:tableColumn id="3" name="URL"/>
+    <x:tableColumn id="4" name="Recommendation"/>
+    <x:tableColumn id="5" name="Priority"/>
+    <x:tableColumn id="6" name="Estimated Effort"/>
+    <x:tableColumn id="7" name="Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -479,13 +635,18 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17.200000762939453" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.600000381469727" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="36" customHeight="1">
+    <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>CRO and UX Findings</x:v>
+        <x:v>CRO and UX Findings - CRO &amp; UX Findings</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -493,11 +654,10 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    </x:row>
+    <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Traffic Radius enterprise SEO evidence register ? professional V18-compatible v19 edition</x:v>
+        <x:v>Behavioural conclusions withheld until GA4 is connected.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -505,129 +665,661 @@
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Control</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Canonical value</x:v>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Evidence as of 2026-07-15 | Domain kakawachocolates.com.au | Run KAKAWA-ENT-20260715 | EVIDENCE-LINKED</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Finding ID</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Finding</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Impact</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="J5" s="13" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="K5" s="13" t="str">
+        <x:v>Rows</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="10" t="str">
-        <x:v>Evidence as of</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>2026-07-15</x:v>
+      <x:c r="A6" s="9" t="str">
+        <x:v>F-001</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>technical</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>HTTP 404 response</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>Observed on 42 of 357 fetched pages; review before deployment.</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>The crawled URL did not return a successful or redirect response.</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="str">
+        <x:v>EV-0155, EV-0199, EV-0204, EV-0205, EV-0208, EV-0209, EV-0219, EV-0222, EV-0223, EV-0226, EV-0231, EV-0235, EV-0241, EV-0258, EV-0259, EV-0261, EV-0266, EV-0267, EV-0268, EV-0269, EV-0270, EV-0271, EV-0272, EV-0273, EV-0274, EV-0328, EV-0329, EV-0330, EV-0331, EV-0332, EV-0333, EV-0337, EV-0338, EV-0339, EV-0340, EV-0341, EV-0342, EV-0343, EV-0344, EV-0345, EV-0346, EV-0347</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:f>COUNTIF(E6:E30,J6)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="10" t="str">
-        <x:v>Approved domain</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>kakawachocolates.com.au</x:v>
+      <x:c r="A7" s="9" t="str">
+        <x:v>F-004</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>on_page</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Missing primary heading</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>Observed on 2 of 357 fetched pages; review before deployment.</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str">
+        <x:v>The successful HTML page has no non-empty H1 heading.</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="str">
+        <x:v>EV-0020, EV-0025</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:f>COUNTIF(E6:E30,J7)</x:f>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="10" t="str">
-        <x:v>Run</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>KAKAWA-ENT-20260715</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>F-003</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>on_page</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Missing meta description</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>Observed on 12 of 357 fetched pages; review before deployment.</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>The successful HTML page has no non-empty meta description.</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
+        <x:v>EV-0004, EV-0020, EV-0079, EV-0080, EV-0278, EV-0279, EV-0280, EV-0348, EV-0349, EV-0350, EV-0352, EV-0353</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:f>COUNTIF(E6:E30,J8)</x:f>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="10" t="str">
-        <x:v>Evidence status</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>EVIDENCE-LINKED</x:v>
+      <x:c r="A9" s="9" t="str">
+        <x:v>F-005</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>on_page</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Multiple primary headings</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>Observed on 3 of 357 fetched pages; review before deployment.</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str">
+        <x:v>The page contains 2 non-empty H1 headings and needs editorial review.</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="str">
+        <x:v>EV-0056, EV-0059, EV-0064</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:f>COUNTIF(E6:E30,J9)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="10" t="str">
-        <x:v>Decision</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>Review and approve before implementation.</x:v>
+      <x:c r="A10" s="9" t="str">
+        <x:v>F-002</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>on_page</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Long document title</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>Observed on 62 of 357 fetched pages; review before deployment.</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>The title is longer than the configured 65-character editorial review threshold.</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
+        <x:v>EV-0001, EV-0006, EV-0008, EV-0011, EV-0017, EV-0022, EV-0023, EV-0024, EV-0033, EV-0038, EV-0048, EV-0055, EV-0057, EV-0058, EV-0060, EV-0062, EV-0063, EV-0064, EV-0065, EV-0068, EV-0071, EV-0076, EV-0077, EV-0095, EV-0129, EV-0143, EV-0145, EV-0146, EV-0156, EV-0193, EV-0194, EV-0197, EV-0198, EV-0201, EV-0203, EV-0206, EV-0207, EV-0216, EV-0217, EV-0218, EV-0221, EV-0228, EV-0230, EV-0237, EV-0238, EV-0239, EV-0240, EV-0247, EV-0248, EV-0253, EV-0260, EV-0292, EV-0294, EV-0295, EV-0308, EV-0313, EV-0314, EV-0315, EV-0322, EV-0327, EV-0336, EV-0357</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="10" t="str">
-        <x:v>Record count</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="n">
-        <x:f>MAX(0,COUNTA(Register!A6:A1000))</x:f>
-        <x:v>5</x:v>
+      <x:c r="A11" s="9" t="str">
+        <x:v>CRO-001</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="str">
+        <x:v>EV-0001, EV-FACT-02, EV-FACT-03</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="10" t="str">
-        <x:v>Release class</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:f>IF(B11&gt;0,"REVIEW READY","UNAVAILABLE")</x:f>
-        <x:v>REVIEW READY</x:v>
+      <x:c r="A12" s="9" t="str">
+        <x:v>CRO-002</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/gift-boxes</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
+        <x:v>EV-0011, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>CRO-003</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/chocolate-bar</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="str">
+        <x:v>EV-0006, EV-FACT-02</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12" t="str">
-        <x:v>Quality gate</x:v>
-      </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C14" t="str"/>
-      <x:c r="D14" t="str"/>
-      <x:c r="E14" t="str"/>
-      <x:c r="F14" t="str"/>
+      <x:c r="A14" s="9" t="str">
+        <x:v>CRO-004</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/pralines-bonbons</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="str">
+        <x:v>EV-0017, EV-FACT-02</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Evidence-linked</x:v>
-      </x:c>
-      <x:c r="B15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" t="str"/>
-      <x:c r="D15" t="str"/>
-      <x:c r="E15" t="str"/>
-      <x:c r="F15" t="str"/>
+      <x:c r="A15" s="9" t="str">
+        <x:v>CRO-005</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/chocolate-slab</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F15" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="str">
+        <x:v>EV-0008, EV-FACT-02</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>Approval required</x:v>
-      </x:c>
-      <x:c r="B16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" t="str"/>
-      <x:c r="D16" t="str"/>
-      <x:c r="E16" t="str"/>
-      <x:c r="F16" t="str"/>
+      <x:c r="A16" s="9" t="str">
+        <x:v>CRO-006</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/single-origin-chocolates</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F16" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="str">
+        <x:v>EV-0018, EV-FACT-02</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>Fabricated substitutes</x:v>
-      </x:c>
-      <x:c r="B17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" t="str"/>
-      <x:c r="D17" t="str"/>
-      <x:c r="E17" t="str"/>
-      <x:c r="F17" t="str"/>
+      <x:c r="A17" s="9" t="str">
+        <x:v>CRO-007</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/design-your-own-box</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F17" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="str">
+        <x:v>EV-0081, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="9" t="str">
+        <x:v>CRO-008</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/confectionary</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F18" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="str">
+        <x:v>EV-0009, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="9" t="str">
+        <x:v>CRO-009</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/corporate-chocolates</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F19" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="str">
+        <x:v>EV-0022, EV-FACT-02, EV-FACT-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="9" t="str">
+        <x:v>CRO-010</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/events-corporates</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="str">
+        <x:v>EV-0023, EV-FACT-02, EV-FACT-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="9" t="str">
+        <x:v>CRO-011</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/wedding-chocolates</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="str">
+        <x:v>EV-0033, EV-FACT-02, EV-FACT-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="9" t="str">
+        <x:v>CRO-012</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/wholesale</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="str">
+        <x:v>EV-0034, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="9" t="str">
+        <x:v>CRO-013</x:v>
+      </x:c>
+      <x:c r="B23" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/shipping</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F23" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="str">
+        <x:v>EV-0031, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="9" t="str">
+        <x:v>CRO-014</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/about-us</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="str">
+        <x:v>EV-0020, EV-FACT-02, EV-FACT-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="9" t="str">
+        <x:v>CRO-015</x:v>
+      </x:c>
+      <x:c r="B25" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C25" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/how-we-make-chocolate</x:v>
+      </x:c>
+      <x:c r="D25" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F25" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="str">
+        <x:v>EV-0024, EV-FACT-02, EV-FACT-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="9" t="str">
+        <x:v>CRO-016</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/our-ingredients-and-ethics</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="str">
+        <x:v>EV-0026, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="9" t="str">
+        <x:v>CRO-017</x:v>
+      </x:c>
+      <x:c r="B27" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C27" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/pages/membership</x:v>
+      </x:c>
+      <x:c r="D27" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E27" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F27" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="str">
+        <x:v>EV-0025, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="9" t="str">
+        <x:v>CRO-018</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/blogs/chocolates</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="str">
+        <x:v>EV-0002, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="9" t="str">
+        <x:v>CRO-019</x:v>
+      </x:c>
+      <x:c r="B29" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C29" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/christmas</x:v>
+      </x:c>
+      <x:c r="D29" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E29" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F29" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="str">
+        <x:v>EV-0193, EV-FACT-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="9" t="str">
+        <x:v>CRO-020</x:v>
+      </x:c>
+      <x:c r="B30" s="9" t="str">
+        <x:v>Decision clarity</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="str">
+        <x:v>Review CTA and hierarchy for https://kakawachocolates.com.au/collections/easter</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="str">
+        <x:v>Manual and GA4 validation required</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="str">
+        <x:v>Align one next action to the approved intent.</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="str">
+        <x:v>EV-0194, EV-FACT-02</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ee418fb80434e02"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a71d3d40bc4083"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3af5bc7bbc614ef7"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -635,31 +1327,29 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34.20000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.600000381469727" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="13" t="str">
-        <x:v>CRO and UX Findings</x:v>
-      </x:c>
-      <x:c r="B1" s="13"/>
-      <x:c r="C1" s="13"/>
-      <x:c r="D1" s="13"/>
-      <x:c r="E1" s="13"/>
-      <x:c r="F1" s="13"/>
-      <x:c r="G1" s="13"/>
-      <x:c r="H1" s="13"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>CRO and UX Findings - Quick Wins</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Canonical values only. Unavailable evidence is labelled explicitly; no estimates or fabricated substitutes.</x:v>
+        <x:v>Low-risk review queue; not a forecast.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -667,172 +1357,361 @@
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>ID</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Evidence as of 2026-07-15 | Domain kakawachocolates.com.au | Run KAKAWA-ENT-20260715 | EVIDENCE-LINKED</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Finding ID</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>URL</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
         <x:v>Priority</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Category</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>Finding</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>Impact</x:v>
-      </x:c>
-      <x:c r="F5" s="14" t="str">
-        <x:v>Confidence</x:v>
-      </x:c>
-      <x:c r="G5" s="14" t="str">
-        <x:v>Approval</x:v>
-      </x:c>
-      <x:c r="H5" s="14" t="str">
+      <x:c r="F5" s="11" t="str">
+        <x:v>Estimated Effort</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
         <x:v>Evidence</x:v>
       </x:c>
+      <x:c r="J5" s="13" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="K5" s="13" t="str">
+        <x:v>Rows</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>F-001</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
+      <x:c r="A6" s="9" t="str">
+        <x:v>QW-019</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/pages/about-us</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>Resolve Review, Missing and Missing</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="str">
+        <x:v>EV-0020</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:f>COUNTIF(E6:E17,J6)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>QW-024</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/pages/membership</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>Resolve Review, Review and Missing</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="str">
+        <x:v>EV-0025</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>technical</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>HTTP 404 response</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Observed on 42 of 357 fetched pages; review before deployment.</x:v>
-      </x:c>
-      <x:c r="F6" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>analyst</x:v>
-      </x:c>
-      <x:c r="H6" s="14" t="str">
-        <x:v>EV-0155, EV-0199, EV-0204, EV-0205, EV-0208, EV-0209, EV-0219, EV-0222, EV-0223, EV-0226, EV-0231, EV-0235, EV-0241, EV-0258, EV-0259, EV-0261, EV-0266, EV-0267, EV-0268, EV-0269, EV-0270, EV-0271, EV-0272, EV-0273, EV-0274, EV-0328, EV-0329, EV-0330, EV-0331, EV-0332, EV-0333, EV-0337, EV-0338, EV-0339, EV-0340, EV-0341, EV-0342, EV-0343, EV-0344, EV-0345, EV-0346, EV-0347</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>F-004</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>on_page</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>Missing primary heading</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>Observed on 2 of 357 fetched pages; review before deployment.</x:v>
-      </x:c>
-      <x:c r="F7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" s="14" t="str">
-        <x:v>analyst</x:v>
-      </x:c>
-      <x:c r="H7" s="14" t="str">
-        <x:v>EV-0020, EV-0025</x:v>
+      <x:c r="K7" t="n">
+        <x:f>COUNTIF(E6:E17,J7)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>F-003</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>on_page</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>Missing meta description</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>Observed on 12 of 357 fetched pages; review before deployment.</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>analyst</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="str">
-        <x:v>EV-0004, EV-0020, EV-0079, EV-0080, EV-0278, EV-0279, EV-0280, EV-0348, EV-0349, EV-0350, EV-0352, EV-0353</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>QW-078</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="str">
+        <x:v>EV-0079</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:f>COUNTIF(E6:E17,J8)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>F-005</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>on_page</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>Multiple primary headings</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>Observed on 3 of 357 fetched pages; review before deployment.</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>analyst</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="str">
-        <x:v>EV-0056, EV-0059, EV-0064</x:v>
+      <x:c r="A9" s="9" t="str">
+        <x:v>QW-079</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/policies/shipping-policy</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="str">
+        <x:v>EV-0080</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:f>COUNTIF(E6:E17,J9)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>F-002</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>P3</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>on_page</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>Long document title</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>Observed on 62 of 357 fetched pages; review before deployment.</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="str">
-        <x:v>analyst</x:v>
-      </x:c>
-      <x:c r="H10" s="14" t="str">
-        <x:v>EV-0001, EV-0006, EV-0008, EV-0011, EV-0017, EV-0022, EV-0023, EV-0024, EV-0033, EV-0038, EV-0048, EV-0055, EV-0057, EV-0058, EV-0060, EV-0062, EV-0063, EV-0064, EV-0065, EV-0068, EV-0071, EV-0076, EV-0077, EV-0095, EV-0129, EV-0143, EV-0145, EV-0146, EV-0156, EV-0193, EV-0194, EV-0197, EV-0198, EV-0201, EV-0203, EV-0206, EV-0207, EV-0216, EV-0217, EV-0218, EV-0221, EV-0228, EV-0230, EV-0237, EV-0238, EV-0239, EV-0240, EV-0247, EV-0248, EV-0253, EV-0260, EV-0292, EV-0294, EV-0295, EV-0308, EV-0313, EV-0314, EV-0315, EV-0322, EV-0327, EV-0336, EV-0357</x:v>
+      <x:c r="A10" s="9" t="str">
+        <x:v>QW-252</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=2</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="str">
+        <x:v>EV-0278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>QW-253</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=3</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="str">
+        <x:v>EV-0279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>QW-254</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=8</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="str">
+        <x:v>EV-0280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>QW-305</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=1</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="str">
+        <x:v>EV-0348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="str">
+        <x:v>QW-306</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=4</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="str">
+        <x:v>EV-0349</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="9" t="str">
+        <x:v>QW-307</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=5</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F15" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="str">
+        <x:v>EV-0350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="9" t="str">
+        <x:v>QW-309</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=6</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F16" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="str">
+        <x:v>EV-0352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="9" t="str">
+        <x:v>QW-310</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>On-page clarity</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>https://kakawachocolates.com.au/collections/all?page=7</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="str">
+        <x:v>Resolve Review, Missing and Review</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F17" s="9" t="str">
+        <x:v>Low-medium</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="str">
+        <x:v>EV-0353</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd8fa18cdf9f4a44"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra207181969d84ae8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d3a8884d7234f0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>